--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1205,7 +1205,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>112</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>119</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>124</v>
       </c>
@@ -2144,12 +2144,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK13">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
+++ b/release-branch/StructureDefinition-bc-death-verified-flag-history-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
